--- a/PRUEBAS DE CONFIANZA.xlsx
+++ b/PRUEBAS DE CONFIANZA.xlsx
@@ -8,13 +8,27 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\omich\Documents\SolucionesEnergeticasParaWSN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A8293AF-00D1-4A9C-803F-AE43557A6D1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD53621D-E13A-4CC6-B5BA-216BF938F714}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{FF7E538C-BC1E-4233-9CFA-651CC43E1462}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlchart.v1.0" hidden="1">Hoja1!$A$13:$C$13</definedName>
+    <definedName name="_xlchart.v1.1" hidden="1">Hoja1!$A$22:$C$22</definedName>
+    <definedName name="_xlchart.v1.10" hidden="1">(Hoja1!$H$4:$H$11,Hoja1!$H$13:$H$20,Hoja1!$H$22:$H$29)</definedName>
+    <definedName name="_xlchart.v1.11" hidden="1">Hoja1!$H$3</definedName>
+    <definedName name="_xlchart.v1.2" hidden="1">Hoja1!$B$4:$D$4</definedName>
+    <definedName name="_xlchart.v1.3" hidden="1">Hoja1!$D$13:$G$13</definedName>
+    <definedName name="_xlchart.v1.4" hidden="1">Hoja1!$D$22:$G$22</definedName>
+    <definedName name="_xlchart.v1.5" hidden="1">Hoja1!$E$4:$G$4</definedName>
+    <definedName name="_xlchart.v1.6" hidden="1">(Hoja1!$C$4:$C$11,Hoja1!$C$13:$C$20,Hoja1!$C$22:$C$29)</definedName>
+    <definedName name="_xlchart.v1.7" hidden="1">(Hoja1!$H$4:$H$11,Hoja1!$H$13:$H$20,Hoja1!$H$22:$H$29)</definedName>
+    <definedName name="_xlchart.v1.8" hidden="1">Hoja1!$H$3</definedName>
+    <definedName name="_xlchart.v1.9" hidden="1">(Hoja1!$C$4:$C$11,Hoja1!$C$13:$C$20,Hoja1!$C$22:$C$29)</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -39,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="26">
   <si>
     <t>SOFTWARE</t>
   </si>
@@ -100,6 +114,24 @@
   <si>
     <t>LoRa</t>
   </si>
+  <si>
+    <t>TASA DE ÉXITO</t>
+  </si>
+  <si>
+    <t>PAQUETES POR SEGUNDO</t>
+  </si>
+  <si>
+    <t>PAQUETES POR MINUTO</t>
+  </si>
+  <si>
+    <t>EFICIENCIA DE ENVIO</t>
+  </si>
+  <si>
+    <t>PAQUETES PÉRDIDOS</t>
+  </si>
+  <si>
+    <t>|</t>
+  </si>
 </sst>
 </file>
 
@@ -128,7 +160,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -156,6 +188,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -187,7 +225,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -198,6 +236,11 @@
     <xf numFmtId="2" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -213,6 +256,6473 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="es-ES"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="106"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="6"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx2"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="es-MX"/>
+              <a:t>Porcentaje de pérdida NRF24L01</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx2"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="es-MX"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:gradFill rotWithShape="1">
+              <a:gsLst>
+                <a:gs pos="0">
+                  <a:schemeClr val="accent4">
+                    <a:satMod val="103000"/>
+                    <a:lumMod val="102000"/>
+                    <a:tint val="94000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="50000">
+                  <a:schemeClr val="accent4">
+                    <a:satMod val="110000"/>
+                    <a:lumMod val="100000"/>
+                    <a:shade val="100000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="100000">
+                  <a:schemeClr val="accent4">
+                    <a:lumMod val="99000"/>
+                    <a:satMod val="120000"/>
+                    <a:shade val="78000"/>
+                  </a:schemeClr>
+                </a:gs>
+              </a:gsLst>
+              <a:lin ang="5400000" scaled="0"/>
+            </a:gradFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Hoja1!$B$4:$B$11</c:f>
+              <c:strCache>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>BASICO</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>ADAPTIVE</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>ENERGY</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>ENERGY + ADAPTIVE</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>ADAPTIVE + CODEC</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>CODEC</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>CODEC + ENERGY</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>CODEC + ENERGY + ADAPTIVE</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Hoja1!$H$4:$H$11</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.3333333333333335</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.46511627906976744</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.57471264367816088</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1.5151515151515151</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>4</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-2551-45D5-BB1D-2EC164617630}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="100"/>
+        <c:overlap val="-24"/>
+        <c:axId val="475875935"/>
+        <c:axId val="475877855"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="475875935"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx2">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx2"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-MX"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="475877855"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="475877855"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx2">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0.00" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx2"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-MX"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="475875935"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx2"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="es-MX"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx2">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="es-MX"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="es-ES"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="108"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="8"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx2"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="es-MX"/>
+              <a:t>Porcentaje de pérdida XBEE</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx2"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="es-MX"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="stacked"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:gradFill rotWithShape="1">
+              <a:gsLst>
+                <a:gs pos="0">
+                  <a:schemeClr val="accent6">
+                    <a:satMod val="103000"/>
+                    <a:lumMod val="102000"/>
+                    <a:tint val="94000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="50000">
+                  <a:schemeClr val="accent6">
+                    <a:satMod val="110000"/>
+                    <a:lumMod val="100000"/>
+                    <a:shade val="100000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="100000">
+                  <a:schemeClr val="accent6">
+                    <a:lumMod val="99000"/>
+                    <a:satMod val="120000"/>
+                    <a:shade val="78000"/>
+                  </a:schemeClr>
+                </a:gs>
+              </a:gsLst>
+              <a:lin ang="5400000" scaled="0"/>
+            </a:gradFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Hoja1!$B$13:$B$20</c:f>
+              <c:strCache>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>BASICO</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>ADAPTIVE</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>ENERGY</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>ENERGY + ADAPTIVE</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>ADAPTIVE + CODEC</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>CODEC</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>CODEC + ENERGY</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>CODEC + ENERGY + ADAPTIVE</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Hoja1!$H$13:$H$20</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>16.176470588235293</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3.3898305084745761</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2.4390243902439024</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>7.0000000000000009</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.94339622641509435</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2.6402640264026402</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>3.8461538461538463</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>3.8461538461538463</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-14C2-4EE9-BE8C-48D2BC6A8A2D}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="150"/>
+        <c:overlap val="100"/>
+        <c:axId val="451559567"/>
+        <c:axId val="451556207"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="451559567"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx2">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx2"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-MX"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="451556207"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="451556207"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx2">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0.00" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx2"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-MX"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="451559567"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx2">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="es-MX"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="es-ES"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="107"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="7"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx2"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="es-MX"/>
+              <a:t>Porcentaje</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="es-MX" baseline="0"/>
+              <a:t> de pérdida LoRa</a:t>
+            </a:r>
+            <a:endParaRPr lang="es-MX"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx2"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="es-MX"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:gradFill rotWithShape="1">
+              <a:gsLst>
+                <a:gs pos="0">
+                  <a:schemeClr val="accent5">
+                    <a:satMod val="103000"/>
+                    <a:lumMod val="102000"/>
+                    <a:tint val="94000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="50000">
+                  <a:schemeClr val="accent5">
+                    <a:satMod val="110000"/>
+                    <a:lumMod val="100000"/>
+                    <a:shade val="100000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="100000">
+                  <a:schemeClr val="accent5">
+                    <a:lumMod val="99000"/>
+                    <a:satMod val="120000"/>
+                    <a:shade val="78000"/>
+                  </a:schemeClr>
+                </a:gs>
+              </a:gsLst>
+              <a:lin ang="5400000" scaled="0"/>
+            </a:gradFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Hoja1!$B$22:$B$29</c:f>
+              <c:strCache>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>BASICO</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>ADAPTIVE</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>ENERGY</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>ENERGY + ADAPTIVE</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>ADAPTIVE + CODEC</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>CODEC</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>CODEC + ENERGY</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>CODEC + ENERGY + ADAPTIVE</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Hoja1!$H$22:$H$29</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.5</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2.6315789473684208</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1.5789473684210527</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1.0695187165775399</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1.0050251256281406</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.5</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-E11C-49DA-AA78-5DCB5AFCCD57}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="100"/>
+        <c:overlap val="-24"/>
+        <c:axId val="593497231"/>
+        <c:axId val="593498671"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="593497231"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx2">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx2"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-MX"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="593498671"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="593498671"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx2">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0.00" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx2"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-MX"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="593497231"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx2">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="es-MX"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="es-ES"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="es-MX"/>
+              <a:t>Integridad</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="es-MX" baseline="0"/>
+              <a:t> de envío NRF24L01</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="es-MX"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="percentStacked"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Hoja1!$F$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>PAQUETES RECIBIDOS</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent6"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Hoja1!$B$4:$B$11</c:f>
+              <c:strCache>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>BASICO</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>ADAPTIVE</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>ENERGY</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>ENERGY + ADAPTIVE</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>ADAPTIVE + CODEC</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>CODEC</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>CODEC + ENERGY</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>CODEC + ENERGY + ADAPTIVE</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Hoja1!$F$4:$F$11</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>199</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>148</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>214</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>138</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>346</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>198</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>130</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>192</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-5625-4267-B464-A7F2DEFD502D}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Hoja1!$G$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>PAQUETES PERDIDOS</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="FF0000"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Hoja1!$B$4:$B$11</c:f>
+              <c:strCache>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>BASICO</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>ADAPTIVE</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>ENERGY</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>ENERGY + ADAPTIVE</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>ADAPTIVE + CODEC</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>CODEC</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>CODEC + ENERGY</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>CODEC + ENERGY + ADAPTIVE</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Hoja1!$G$4:$G$11</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-5625-4267-B464-A7F2DEFD502D}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="150"/>
+        <c:overlap val="100"/>
+        <c:axId val="483679375"/>
+        <c:axId val="483680815"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="483679375"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-MX"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="483680815"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="483680815"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0%" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-MX"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="483679375"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="es-MX"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="es-MX"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="es-ES"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="es-MX"/>
+              <a:t>Integridad</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="es-MX" baseline="0"/>
+              <a:t> de envío XBEE</a:t>
+            </a:r>
+            <a:endParaRPr lang="es-MX"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="es-MX"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="percentStacked"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Hoja1!$F$12</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>PAQUETES RECIBIDOS</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Hoja1!$B$13:$B$20</c:f>
+              <c:strCache>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>BASICO</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>ADAPTIVE</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>ENERGY</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>ENERGY + ADAPTIVE</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>ADAPTIVE + CODEC</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>CODEC</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>CODEC + ENERGY</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>CODEC + ENERGY + ADAPTIVE</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Hoja1!$F$13:$F$20</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>171</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>285</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>200</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>93</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>210</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>295</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>200</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>200</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-6F66-4392-9193-A8EF4E487159}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Hoja1!$G$12</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>PAQUETES PÉRDIDOS</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Hoja1!$B$13:$B$20</c:f>
+              <c:strCache>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>BASICO</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>ADAPTIVE</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>ENERGY</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>ENERGY + ADAPTIVE</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>ADAPTIVE + CODEC</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>CODEC</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>CODEC + ENERGY</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>CODEC + ENERGY + ADAPTIVE</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Hoja1!$G$13:$G$20</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>33</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-6F66-4392-9193-A8EF4E487159}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="150"/>
+        <c:overlap val="100"/>
+        <c:axId val="649345247"/>
+        <c:axId val="649342847"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="649345247"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-MX"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="649342847"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="649342847"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0%" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-MX"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="649345247"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="es-MX"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="es-MX"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="es-ES"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="es-MX"/>
+              <a:t>Integridad</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="es-MX" baseline="0"/>
+              <a:t> de envío LoRa</a:t>
+            </a:r>
+            <a:endParaRPr lang="es-MX"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="es-MX"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="percentStacked"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Hoja1!$F$21</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>PAQUETES RECIBIDOS</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="00B0F0"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Hoja1!$B$22:$B$29</c:f>
+              <c:strCache>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>BASICO</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>ADAPTIVE</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>ENERGY</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>ENERGY + ADAPTIVE</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>ADAPTIVE + CODEC</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>CODEC</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>CODEC + ENERGY</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>CODEC + ENERGY + ADAPTIVE</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Hoja1!$F$22:$F$29</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>190</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>200</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>199</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>185</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>187</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>185</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>197</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>199</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-813B-42A8-A464-769854F87BBA}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Hoja1!$G$21</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>PAQUETES PÉRDIDOS</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="FF0000"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Hoja1!$B$22:$B$29</c:f>
+              <c:strCache>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>BASICO</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>ADAPTIVE</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>ENERGY</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>ENERGY + ADAPTIVE</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>ADAPTIVE + CODEC</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>CODEC</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>CODEC + ENERGY</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>CODEC + ENERGY + ADAPTIVE</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Hoja1!$G$22:$G$29</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-813B-42A8-A464-769854F87BBA}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="150"/>
+        <c:overlap val="100"/>
+        <c:axId val="649333727"/>
+        <c:axId val="649341887"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="649333727"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-MX"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="649341887"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="649341887"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0%" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-MX"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="649333727"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="es-MX"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="es-MX"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chartEx1.xml><?xml version="1.0" encoding="utf-8"?>
+<cx:chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex">
+  <cx:chartData>
+    <cx:data id="0">
+      <cx:strDim type="cat">
+        <cx:f>_xlchart.v1.6</cx:f>
+      </cx:strDim>
+      <cx:numDim type="val">
+        <cx:f>_xlchart.v1.7</cx:f>
+      </cx:numDim>
+    </cx:data>
+  </cx:chartData>
+  <cx:chart>
+    <cx:title pos="t" align="ctr" overlay="0">
+      <cx:tx>
+        <cx:txData>
+          <cx:v>Estabilidad del Radio</cx:v>
+        </cx:txData>
+      </cx:tx>
+      <cx:txPr>
+        <a:bodyPr spcFirstLastPara="1" vertOverflow="ellipsis" horzOverflow="overflow" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr" rtl="0">
+            <a:defRPr/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="es-ES" sz="1400" b="0" i="0" u="none" strike="noStrike" baseline="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:sysClr>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
+            </a:rPr>
+            <a:t>Estabilidad del Radio</a:t>
+          </a:r>
+        </a:p>
+      </cx:txPr>
+    </cx:title>
+    <cx:plotArea>
+      <cx:plotAreaRegion>
+        <cx:series layoutId="boxWhisker" uniqueId="{F7133788-1129-4FB7-B5EE-355D2AD50E0E}">
+          <cx:tx>
+            <cx:txData>
+              <cx:f>_xlchart.v1.8</cx:f>
+              <cx:v>PORCENTAJE DE PÉRDIDA</cx:v>
+            </cx:txData>
+          </cx:tx>
+          <cx:dataId val="0"/>
+          <cx:layoutPr>
+            <cx:visibility meanLine="0" meanMarker="0" nonoutliers="0" outliers="1"/>
+            <cx:statistics quartileMethod="exclusive"/>
+          </cx:layoutPr>
+        </cx:series>
+      </cx:plotAreaRegion>
+      <cx:axis id="0">
+        <cx:catScaling gapWidth="1.10000002"/>
+        <cx:tickLabels/>
+      </cx:axis>
+      <cx:axis id="1">
+        <cx:valScaling/>
+        <cx:majorGridlines/>
+        <cx:tickLabels/>
+      </cx:axis>
+    </cx:plotArea>
+    <cx:legend pos="t" align="ctr" overlay="0"/>
+  </cx:chart>
+</cx:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="withinLinearReversed" id="24">
+  <a:schemeClr val="accent4"/>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="withinLinear" id="19">
+  <a:schemeClr val="accent6"/>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="withinLinear" id="18">
+  <a:schemeClr val="accent5"/>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors5.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors6.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors7.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="207">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:defRPr sz="900" b="1" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk2">
+        <a:lumMod val="75000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="3">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="2"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="3">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="2"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="3"/>
+    <cs:effectRef idx="2"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="31750" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="3">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="2"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="12700">
+        <a:solidFill>
+          <a:schemeClr val="lt2"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="6"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="3"/>
+    <cs:effectRef idx="2"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:prstDash val="dash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:prstDash val="dash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:prstDash val="dash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:defRPr sz="1600" b="1" kern="1200"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="302">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:defRPr sz="900" b="1" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk2">
+        <a:lumMod val="75000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="3">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="2"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="3">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="2"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="3"/>
+    <cs:effectRef idx="2"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="31750" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="3">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="2"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="12700">
+        <a:solidFill>
+          <a:schemeClr val="lt2"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="6"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="3"/>
+    <cs:effectRef idx="2"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:prstDash val="dash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:prstDash val="dash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:prstDash val="dash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:defRPr sz="1600" b="1" kern="1200"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="207">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:defRPr sz="900" b="1" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk2">
+        <a:lumMod val="75000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="3">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="2"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="3">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="2"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="3"/>
+    <cs:effectRef idx="2"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="31750" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="3">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="2"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="12700">
+        <a:solidFill>
+          <a:schemeClr val="lt2"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="6"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="3"/>
+    <cs:effectRef idx="2"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:prstDash val="dash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:prstDash val="dash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:prstDash val="dash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:defRPr sz="1600" b="1" kern="1200"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="297">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style5.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="297">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style6.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="297">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style7.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="407">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" b="1"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:effectLst>
+        <a:innerShdw blurRad="114300">
+          <a:schemeClr val="phClr"/>
+        </a:innerShdw>
+      </a:effectLst>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="6"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+            <a:lumOff val="10000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat">
+        <a:solidFill>
+          <a:srgbClr val="D9D9D9"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="50000"/>
+        <a:lumOff val="50000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1800" b="1" cap="all" spc="150"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>987380</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>53662</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>692631</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>182450</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Gráfico 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{76244706-681F-670B-1D2C-4B3A29AAD2C0}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>994318</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>180279</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>557562</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>135674</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="4" name="Gráfico 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DDB17FCC-65A1-69C7-242B-E84ED0FC9469}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>13010</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>631902</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>154259</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="5" name="Gráfico 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0744FDC2-8874-841E-A94E-40BCEF40B86E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>1191296</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>12878</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>547353</xdr:colOff>
+      <xdr:row>61</xdr:row>
+      <xdr:rowOff>19318</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="14" name="Gráfico 13">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CE9B73C0-3CB2-18DF-C292-08DCCA0D9B2B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>1223492</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>12880</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>472224</xdr:colOff>
+      <xdr:row>61</xdr:row>
+      <xdr:rowOff>19319</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="15" name="Gráfico 14">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7731B656-42A2-D044-0EE1-EC70EC6FDE97}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>34343</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>622479</xdr:colOff>
+      <xdr:row>60</xdr:row>
+      <xdr:rowOff>40782</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="16" name="Gráfico 15">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{07976773-7094-A7D3-0DAA-9AA51F578D27}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId6"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>53662</xdr:colOff>
+      <xdr:row>61</xdr:row>
+      <xdr:rowOff>141667</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>676141</xdr:colOff>
+      <xdr:row>76</xdr:row>
+      <xdr:rowOff>148107</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" Requires="cx1">
+        <xdr:graphicFrame macro="">
+          <xdr:nvGraphicFramePr>
+            <xdr:cNvPr id="21" name="Gráfico 20">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DB72914E-4327-86DC-684B-A09FA7B02440}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvGraphicFramePr/>
+          </xdr:nvGraphicFramePr>
+          <xdr:xfrm>
+            <a:off x="0" y="0"/>
+            <a:ext cx="0" cy="0"/>
+          </xdr:xfrm>
+          <a:graphic>
+            <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2014/chartex">
+              <cx:chart xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId7"/>
+            </a:graphicData>
+          </a:graphic>
+        </xdr:graphicFrame>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="0" name=""/>
+            <xdr:cNvSpPr>
+              <a:spLocks noTextEdit="1"/>
+            </xdr:cNvSpPr>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="53662" y="11314090"/>
+              <a:ext cx="4572000" cy="2743200"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:prstClr val="white"/>
+            </a:solidFill>
+            <a:ln w="1">
+              <a:solidFill>
+                <a:prstClr val="green"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:r>
+                <a:rPr lang="es-MX" sz="1100"/>
+                <a:t>Este gráfico no está disponible en su versión de Excel.
+Si edita esta forma o guarda el libro en un formato de archivo diferente, el gráfico no se podrá utilizar.</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -532,19 +7042,23 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC5ECB90-EE67-49F2-B71E-283C8DA9AB5B}">
-  <dimension ref="A3:H27"/>
+  <dimension ref="A3:L51"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.5546875" customWidth="1"/>
     <col min="2" max="2" width="25.33203125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="9.109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="24.109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="24.77734375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="24.109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="28.88671875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="25.44140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="26.44140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="30.44140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="17.44140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="28.109375" customWidth="1"/>
+    <col min="11" max="11" width="30.6640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="25.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:8" ht="18" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:12" ht="18" x14ac:dyDescent="0.35">
       <c r="A3" s="4" t="s">
         <v>18</v>
       </c>
@@ -569,8 +7083,20 @@
       <c r="H3" s="4" t="s">
         <v>5</v>
       </c>
+      <c r="I3" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="J3" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="K3" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="L3" s="9" t="s">
+        <v>23</v>
+      </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>1</v>
       </c>
@@ -597,8 +7123,24 @@
         <f>(G4/E4)*100</f>
         <v>0</v>
       </c>
+      <c r="I4" s="5">
+        <f>100-H4</f>
+        <v>100</v>
+      </c>
+      <c r="J4" s="1">
+        <f>F4/10</f>
+        <v>19.899999999999999</v>
+      </c>
+      <c r="K4" s="5">
+        <f>F4 / 600</f>
+        <v>0.33166666666666667</v>
+      </c>
+      <c r="L4" s="10">
+        <f>F4/E4</f>
+        <v>1</v>
+      </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>2</v>
       </c>
@@ -618,15 +7160,31 @@
         <v>148</v>
       </c>
       <c r="G5" s="1">
-        <f t="shared" ref="G5:G27" si="0">E5-F5</f>
+        <f t="shared" ref="G5:G29" si="0">E5-F5</f>
         <v>2</v>
       </c>
       <c r="H5" s="5">
-        <f t="shared" ref="H5:H27" si="1">(G5/E5)*100</f>
+        <f t="shared" ref="H5:H29" si="1">(G5/E5)*100</f>
         <v>1.3333333333333335</v>
       </c>
+      <c r="I5" s="5">
+        <f t="shared" ref="I5:I29" si="2">100-H5</f>
+        <v>98.666666666666671</v>
+      </c>
+      <c r="J5" s="1">
+        <f t="shared" ref="J5:J29" si="3">F5/10</f>
+        <v>14.8</v>
+      </c>
+      <c r="K5" s="5">
+        <f t="shared" ref="K5:K29" si="4">F5 / 600</f>
+        <v>0.24666666666666667</v>
+      </c>
+      <c r="L5" s="10">
+        <f t="shared" ref="L5:L29" si="5">F5/E5</f>
+        <v>0.98666666666666669</v>
+      </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>3</v>
       </c>
@@ -640,21 +7198,37 @@
         <v>15</v>
       </c>
       <c r="E6" s="1">
-        <v>87</v>
+        <v>215</v>
       </c>
       <c r="F6" s="1">
-        <v>85</v>
+        <v>214</v>
       </c>
       <c r="G6" s="1">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H6" s="5">
         <f t="shared" si="1"/>
-        <v>2.2988505747126435</v>
+        <v>0.46511627906976744</v>
+      </c>
+      <c r="I6" s="5">
+        <f t="shared" si="2"/>
+        <v>99.534883720930239</v>
+      </c>
+      <c r="J6" s="1">
+        <f t="shared" si="3"/>
+        <v>21.4</v>
+      </c>
+      <c r="K6" s="5">
+        <f t="shared" si="4"/>
+        <v>0.35666666666666669</v>
+      </c>
+      <c r="L6" s="10">
+        <f t="shared" si="5"/>
+        <v>0.99534883720930234</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>4</v>
       </c>
@@ -681,8 +7255,24 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
+      <c r="I7" s="5">
+        <f t="shared" si="2"/>
+        <v>100</v>
+      </c>
+      <c r="J7" s="1">
+        <f t="shared" si="3"/>
+        <v>13.8</v>
+      </c>
+      <c r="K7" s="5">
+        <f t="shared" si="4"/>
+        <v>0.23</v>
+      </c>
+      <c r="L7" s="10">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>5</v>
       </c>
@@ -709,8 +7299,24 @@
         <f t="shared" si="1"/>
         <v>0.57471264367816088</v>
       </c>
+      <c r="I8" s="5">
+        <f t="shared" si="2"/>
+        <v>99.425287356321846</v>
+      </c>
+      <c r="J8" s="1">
+        <f t="shared" si="3"/>
+        <v>34.6</v>
+      </c>
+      <c r="K8" s="5">
+        <f t="shared" si="4"/>
+        <v>0.57666666666666666</v>
+      </c>
+      <c r="L8" s="10">
+        <f t="shared" si="5"/>
+        <v>0.99425287356321834</v>
+      </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>6</v>
       </c>
@@ -737,8 +7343,24 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
+      <c r="I9" s="5">
+        <f t="shared" si="2"/>
+        <v>100</v>
+      </c>
+      <c r="J9" s="1">
+        <f t="shared" si="3"/>
+        <v>19.8</v>
+      </c>
+      <c r="K9" s="5">
+        <f t="shared" si="4"/>
+        <v>0.33</v>
+      </c>
+      <c r="L9" s="10">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>7</v>
       </c>
@@ -755,18 +7377,34 @@
         <v>132</v>
       </c>
       <c r="F10" s="1">
-        <v>87</v>
+        <v>130</v>
       </c>
       <c r="G10" s="1">
         <f t="shared" si="0"/>
-        <v>45</v>
+        <v>2</v>
       </c>
       <c r="H10" s="5">
         <f t="shared" si="1"/>
-        <v>34.090909090909086</v>
+        <v>1.5151515151515151</v>
+      </c>
+      <c r="I10" s="5">
+        <f t="shared" si="2"/>
+        <v>98.484848484848484</v>
+      </c>
+      <c r="J10" s="1">
+        <f t="shared" si="3"/>
+        <v>13</v>
+      </c>
+      <c r="K10" s="5">
+        <f t="shared" si="4"/>
+        <v>0.21666666666666667</v>
+      </c>
+      <c r="L10" s="10">
+        <f t="shared" si="5"/>
+        <v>0.98484848484848486</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>8</v>
       </c>
@@ -780,50 +7418,62 @@
         <v>15</v>
       </c>
       <c r="E11" s="1">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="F11" s="1">
-        <v>44</v>
+        <v>192</v>
       </c>
       <c r="G11" s="1">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H11" s="5">
         <f t="shared" si="1"/>
-        <v>12</v>
+        <v>4</v>
+      </c>
+      <c r="I11" s="5">
+        <f t="shared" si="2"/>
+        <v>96</v>
+      </c>
+      <c r="J11" s="1">
+        <f t="shared" si="3"/>
+        <v>19.2</v>
+      </c>
+      <c r="K11" s="5">
+        <f t="shared" si="4"/>
+        <v>0.32</v>
+      </c>
+      <c r="L11" s="10">
+        <f t="shared" si="5"/>
+        <v>0.96</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A12" s="2">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A12" s="1"/>
+      <c r="B12" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C12" s="1"/>
+      <c r="D12" s="1"/>
+      <c r="E12" s="1"/>
+      <c r="F12" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H12" s="5"/>
+      <c r="I12" s="5"/>
+      <c r="J12" s="1"/>
+      <c r="K12" s="5"/>
+      <c r="L12" s="10"/>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A13" s="2">
         <v>9</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B13" s="2" t="s">
         <v>7</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="E12" s="2"/>
-      <c r="F12" s="2"/>
-      <c r="G12" s="2">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H12" s="6" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A13" s="2">
-        <v>10</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>8</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>17</v>
@@ -831,23 +7481,43 @@
       <c r="D13" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="E13" s="2"/>
-      <c r="F13" s="2"/>
+      <c r="E13" s="2">
+        <v>204</v>
+      </c>
+      <c r="F13" s="2">
+        <v>171</v>
+      </c>
       <c r="G13" s="2">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H13" s="6" t="e">
+        <v>33</v>
+      </c>
+      <c r="H13" s="6">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
+        <v>16.176470588235293</v>
+      </c>
+      <c r="I13" s="6">
+        <f t="shared" si="2"/>
+        <v>83.82352941176471</v>
+      </c>
+      <c r="J13" s="2">
+        <f t="shared" si="3"/>
+        <v>17.100000000000001</v>
+      </c>
+      <c r="K13" s="6">
+        <f t="shared" si="4"/>
+        <v>0.28499999999999998</v>
+      </c>
+      <c r="L13" s="6">
+        <f t="shared" si="5"/>
+        <v>0.83823529411764708</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A14" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>17</v>
@@ -855,23 +7525,43 @@
       <c r="D14" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2"/>
+      <c r="E14" s="2">
+        <v>295</v>
+      </c>
+      <c r="F14" s="2">
+        <v>285</v>
+      </c>
       <c r="G14" s="2">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H14" s="6" t="e">
+        <v>10</v>
+      </c>
+      <c r="H14" s="6">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
+        <v>3.3898305084745761</v>
+      </c>
+      <c r="I14" s="6">
+        <f t="shared" si="2"/>
+        <v>96.610169491525426</v>
+      </c>
+      <c r="J14" s="2">
+        <f t="shared" si="3"/>
+        <v>28.5</v>
+      </c>
+      <c r="K14" s="6">
+        <f t="shared" si="4"/>
+        <v>0.47499999999999998</v>
+      </c>
+      <c r="L14" s="6">
+        <f t="shared" si="5"/>
+        <v>0.96610169491525422</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A15" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>17</v>
@@ -879,23 +7569,43 @@
       <c r="D15" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="E15" s="2"/>
-      <c r="F15" s="2"/>
+      <c r="E15" s="2">
+        <v>205</v>
+      </c>
+      <c r="F15" s="2">
+        <v>200</v>
+      </c>
       <c r="G15" s="2">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H15" s="6" t="e">
+        <v>5</v>
+      </c>
+      <c r="H15" s="6">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
+        <v>2.4390243902439024</v>
+      </c>
+      <c r="I15" s="6">
+        <f t="shared" si="2"/>
+        <v>97.560975609756099</v>
+      </c>
+      <c r="J15" s="2">
+        <f t="shared" si="3"/>
+        <v>20</v>
+      </c>
+      <c r="K15" s="6">
+        <f t="shared" si="4"/>
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="L15" s="6">
+        <f t="shared" si="5"/>
+        <v>0.97560975609756095</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A16" s="2">
+        <v>12</v>
+      </c>
+      <c r="B16" s="2" t="s">
         <v>13</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>10</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>17</v>
@@ -903,23 +7613,43 @@
       <c r="D16" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="E16" s="2"/>
-      <c r="F16" s="2"/>
+      <c r="E16" s="2">
+        <v>100</v>
+      </c>
+      <c r="F16" s="2">
+        <v>93</v>
+      </c>
       <c r="G16" s="2">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H16" s="6" t="e">
+        <v>7</v>
+      </c>
+      <c r="H16" s="6">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
+        <v>7.0000000000000009</v>
+      </c>
+      <c r="I16" s="6">
+        <f t="shared" si="2"/>
+        <v>93</v>
+      </c>
+      <c r="J16" s="2">
+        <f t="shared" si="3"/>
+        <v>9.3000000000000007</v>
+      </c>
+      <c r="K16" s="6">
+        <f t="shared" si="4"/>
+        <v>0.155</v>
+      </c>
+      <c r="L16" s="6">
+        <f t="shared" si="5"/>
+        <v>0.93</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A17" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>17</v>
@@ -927,23 +7657,43 @@
       <c r="D17" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="E17" s="2"/>
-      <c r="F17" s="2"/>
+      <c r="E17" s="2">
+        <v>212</v>
+      </c>
+      <c r="F17" s="2">
+        <v>210</v>
+      </c>
       <c r="G17" s="2">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H17" s="6" t="e">
+        <v>2</v>
+      </c>
+      <c r="H17" s="6">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
+        <v>0.94339622641509435</v>
+      </c>
+      <c r="I17" s="6">
+        <f t="shared" si="2"/>
+        <v>99.056603773584911</v>
+      </c>
+      <c r="J17" s="2">
+        <f t="shared" si="3"/>
+        <v>21</v>
+      </c>
+      <c r="K17" s="6">
+        <f t="shared" si="4"/>
+        <v>0.35</v>
+      </c>
+      <c r="L17" s="6">
+        <f t="shared" si="5"/>
+        <v>0.99056603773584906</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A18" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>17</v>
@@ -951,95 +7701,151 @@
       <c r="D18" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="E18" s="2"/>
-      <c r="F18" s="2"/>
+      <c r="E18" s="2">
+        <v>303</v>
+      </c>
+      <c r="F18" s="2">
+        <v>295</v>
+      </c>
       <c r="G18" s="2">
         <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="H18" s="6">
+        <f t="shared" si="1"/>
+        <v>2.6402640264026402</v>
+      </c>
+      <c r="I18" s="6">
+        <f t="shared" si="2"/>
+        <v>97.359735973597367</v>
+      </c>
+      <c r="J18" s="2">
+        <f t="shared" si="3"/>
+        <v>29.5</v>
+      </c>
+      <c r="K18" s="6">
+        <f t="shared" si="4"/>
+        <v>0.49166666666666664</v>
+      </c>
+      <c r="L18" s="6">
+        <f t="shared" si="5"/>
+        <v>0.97359735973597361</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A19" s="2">
+        <v>15</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E19" s="2">
+        <v>208</v>
+      </c>
+      <c r="F19" s="2">
+        <v>200</v>
+      </c>
+      <c r="G19" s="2">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="H19" s="6">
+        <f t="shared" si="1"/>
+        <v>3.8461538461538463</v>
+      </c>
+      <c r="I19" s="6">
+        <f t="shared" si="2"/>
+        <v>96.15384615384616</v>
+      </c>
+      <c r="J19" s="2">
+        <f t="shared" si="3"/>
+        <v>20</v>
+      </c>
+      <c r="K19" s="6">
+        <f t="shared" si="4"/>
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="L19" s="6">
+        <f t="shared" si="5"/>
+        <v>0.96153846153846156</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A20" s="2">
+        <v>16</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E20" s="2">
+        <v>208</v>
+      </c>
+      <c r="F20" s="2">
+        <v>200</v>
+      </c>
+      <c r="G20" s="2">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="H20" s="6">
+        <f t="shared" si="1"/>
+        <v>3.8461538461538463</v>
+      </c>
+      <c r="I20" s="6">
+        <f t="shared" si="2"/>
+        <v>96.15384615384616</v>
+      </c>
+      <c r="J20" s="2">
+        <f t="shared" si="3"/>
+        <v>20</v>
+      </c>
+      <c r="K20" s="6">
+        <f t="shared" si="4"/>
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="L20" s="6">
+        <f t="shared" si="5"/>
+        <v>0.96153846153846156</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A21" s="2"/>
+      <c r="B21" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="H18" s="6" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
+      <c r="C21" s="2"/>
+      <c r="D21" s="2"/>
+      <c r="E21" s="2"/>
+      <c r="F21" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="H21" s="6"/>
+      <c r="I21" s="6"/>
+      <c r="J21" s="2"/>
+      <c r="K21" s="6"/>
+      <c r="L21" s="6"/>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A19" s="3">
-        <v>16</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C19" s="3" t="s">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A22" s="3">
         <v>17</v>
       </c>
-      <c r="D19" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="E19" s="3"/>
-      <c r="F19" s="3"/>
-      <c r="G19" s="3">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H19" s="7" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A20" s="3">
-        <v>17</v>
-      </c>
-      <c r="B20" s="3" t="s">
+      <c r="B22" s="3" t="s">
         <v>7</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="E20" s="3"/>
-      <c r="F20" s="3"/>
-      <c r="G20" s="3">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H20" s="7" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A21" s="3">
-        <v>18</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="E21" s="3"/>
-      <c r="F21" s="3"/>
-      <c r="G21" s="3">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H21" s="7" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A22" s="3">
-        <v>19</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>9</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>19</v>
@@ -1047,23 +7853,43 @@
       <c r="D22" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="E22" s="3"/>
-      <c r="F22" s="3"/>
+      <c r="E22" s="3">
+        <v>200</v>
+      </c>
+      <c r="F22" s="3">
+        <v>190</v>
+      </c>
       <c r="G22" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H22" s="7" t="e">
+        <v>10</v>
+      </c>
+      <c r="H22" s="7">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
+        <v>5</v>
+      </c>
+      <c r="I22" s="7">
+        <f t="shared" si="2"/>
+        <v>95</v>
+      </c>
+      <c r="J22" s="3">
+        <f t="shared" si="3"/>
+        <v>19</v>
+      </c>
+      <c r="K22" s="7">
+        <f t="shared" si="4"/>
+        <v>0.31666666666666665</v>
+      </c>
+      <c r="L22" s="7">
+        <f t="shared" si="5"/>
+        <v>0.95</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A23" s="3">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C23" s="3" t="s">
         <v>19</v>
@@ -1071,23 +7897,43 @@
       <c r="D23" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="E23" s="3"/>
-      <c r="F23" s="3"/>
+      <c r="E23" s="3">
+        <v>200</v>
+      </c>
+      <c r="F23" s="3">
+        <v>200</v>
+      </c>
       <c r="G23" s="3">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H23" s="7" t="e">
+      <c r="H23" s="7">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
+        <v>0</v>
+      </c>
+      <c r="I23" s="7">
+        <f t="shared" si="2"/>
+        <v>100</v>
+      </c>
+      <c r="J23" s="3">
+        <f t="shared" si="3"/>
+        <v>20</v>
+      </c>
+      <c r="K23" s="7">
+        <f t="shared" si="4"/>
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="L23" s="7">
+        <f t="shared" si="5"/>
+        <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A24" s="3">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C24" s="3" t="s">
         <v>19</v>
@@ -1095,23 +7941,43 @@
       <c r="D24" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="E24" s="3"/>
-      <c r="F24" s="3"/>
+      <c r="E24" s="3">
+        <v>200</v>
+      </c>
+      <c r="F24" s="3">
+        <v>199</v>
+      </c>
       <c r="G24" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H24" s="7" t="e">
+        <v>1</v>
+      </c>
+      <c r="H24" s="7">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
+        <v>0.5</v>
+      </c>
+      <c r="I24" s="7">
+        <f t="shared" si="2"/>
+        <v>99.5</v>
+      </c>
+      <c r="J24" s="3">
+        <f t="shared" si="3"/>
+        <v>19.899999999999999</v>
+      </c>
+      <c r="K24" s="7">
+        <f t="shared" si="4"/>
+        <v>0.33166666666666667</v>
+      </c>
+      <c r="L24" s="7">
+        <f t="shared" si="5"/>
+        <v>0.995</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A25" s="3">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C25" s="3" t="s">
         <v>19</v>
@@ -1119,23 +7985,43 @@
       <c r="D25" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="E25" s="3"/>
-      <c r="F25" s="3"/>
+      <c r="E25" s="3">
+        <v>190</v>
+      </c>
+      <c r="F25" s="3">
+        <v>185</v>
+      </c>
       <c r="G25" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H25" s="7" t="e">
+        <v>5</v>
+      </c>
+      <c r="H25" s="7">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
+        <v>2.6315789473684208</v>
+      </c>
+      <c r="I25" s="7">
+        <f t="shared" si="2"/>
+        <v>97.368421052631575</v>
+      </c>
+      <c r="J25" s="3">
+        <f t="shared" si="3"/>
+        <v>18.5</v>
+      </c>
+      <c r="K25" s="7">
+        <f t="shared" si="4"/>
+        <v>0.30833333333333335</v>
+      </c>
+      <c r="L25" s="7">
+        <f t="shared" si="5"/>
+        <v>0.97368421052631582</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A26" s="3">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C26" s="3" t="s">
         <v>19</v>
@@ -1143,23 +8029,43 @@
       <c r="D26" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="E26" s="3"/>
-      <c r="F26" s="3"/>
+      <c r="E26" s="3">
+        <v>190</v>
+      </c>
+      <c r="F26" s="3">
+        <v>187</v>
+      </c>
       <c r="G26" s="3">
-        <f>E26-F26</f>
-        <v>0</v>
-      </c>
-      <c r="H26" s="7" t="e">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="H26" s="7">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
+        <v>1.5789473684210527</v>
+      </c>
+      <c r="I26" s="7">
+        <f t="shared" si="2"/>
+        <v>98.421052631578945</v>
+      </c>
+      <c r="J26" s="3">
+        <f t="shared" si="3"/>
+        <v>18.7</v>
+      </c>
+      <c r="K26" s="7">
+        <f t="shared" si="4"/>
+        <v>0.31166666666666665</v>
+      </c>
+      <c r="L26" s="7">
+        <f t="shared" si="5"/>
+        <v>0.98421052631578942</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A27" s="3">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C27" s="3" t="s">
         <v>19</v>
@@ -1167,20 +8073,134 @@
       <c r="D27" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="E27" s="3"/>
-      <c r="F27" s="3"/>
+      <c r="E27" s="3">
+        <v>187</v>
+      </c>
+      <c r="F27" s="3">
+        <v>185</v>
+      </c>
       <c r="G27" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H27" s="7" t="e">
+        <v>2</v>
+      </c>
+      <c r="H27" s="7">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
+        <v>1.0695187165775399</v>
+      </c>
+      <c r="I27" s="7">
+        <f t="shared" si="2"/>
+        <v>98.930481283422466</v>
+      </c>
+      <c r="J27" s="3">
+        <f t="shared" si="3"/>
+        <v>18.5</v>
+      </c>
+      <c r="K27" s="7">
+        <f t="shared" si="4"/>
+        <v>0.30833333333333335</v>
+      </c>
+      <c r="L27" s="7">
+        <f t="shared" si="5"/>
+        <v>0.98930481283422456</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A28" s="3">
+        <v>23</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E28" s="3">
+        <v>199</v>
+      </c>
+      <c r="F28" s="3">
+        <v>197</v>
+      </c>
+      <c r="G28" s="3">
+        <f>E28-F28</f>
+        <v>2</v>
+      </c>
+      <c r="H28" s="7">
+        <f t="shared" si="1"/>
+        <v>1.0050251256281406</v>
+      </c>
+      <c r="I28" s="7">
+        <f t="shared" si="2"/>
+        <v>98.994974874371863</v>
+      </c>
+      <c r="J28" s="3">
+        <f t="shared" si="3"/>
+        <v>19.7</v>
+      </c>
+      <c r="K28" s="7">
+        <f t="shared" si="4"/>
+        <v>0.32833333333333331</v>
+      </c>
+      <c r="L28" s="7">
+        <f t="shared" si="5"/>
+        <v>0.98994974874371855</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A29" s="3">
+        <v>24</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E29" s="3">
+        <v>200</v>
+      </c>
+      <c r="F29" s="3">
+        <v>199</v>
+      </c>
+      <c r="G29" s="3">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="H29" s="7">
+        <f t="shared" si="1"/>
+        <v>0.5</v>
+      </c>
+      <c r="I29" s="7">
+        <f t="shared" si="2"/>
+        <v>99.5</v>
+      </c>
+      <c r="J29" s="3">
+        <f t="shared" si="3"/>
+        <v>19.899999999999999</v>
+      </c>
+      <c r="K29" s="7">
+        <f t="shared" si="4"/>
+        <v>0.33166666666666667</v>
+      </c>
+      <c r="L29" s="7">
+        <f t="shared" si="5"/>
+        <v>0.995</v>
+      </c>
+    </row>
+    <row r="51" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C51" t="s">
+        <v>25</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/PRUEBAS DE CONFIANZA.xlsx
+++ b/PRUEBAS DE CONFIANZA.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\omich\Documents\SolucionesEnergeticasParaWSN\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\franc\OneDrive\Documentos\SolucionesEnergeticasParaWSN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD53621D-E13A-4CC6-B5BA-216BF938F714}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D08F0AF-5D59-4DBE-B67B-B3FAA497F148}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{FF7E538C-BC1E-4233-9CFA-651CC43E1462}"/>
   </bookViews>
@@ -16,18 +16,9 @@
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlchart.v1.0" hidden="1">Hoja1!$A$13:$C$13</definedName>
-    <definedName name="_xlchart.v1.1" hidden="1">Hoja1!$A$22:$C$22</definedName>
-    <definedName name="_xlchart.v1.10" hidden="1">(Hoja1!$H$4:$H$11,Hoja1!$H$13:$H$20,Hoja1!$H$22:$H$29)</definedName>
-    <definedName name="_xlchart.v1.11" hidden="1">Hoja1!$H$3</definedName>
-    <definedName name="_xlchart.v1.2" hidden="1">Hoja1!$B$4:$D$4</definedName>
-    <definedName name="_xlchart.v1.3" hidden="1">Hoja1!$D$13:$G$13</definedName>
-    <definedName name="_xlchart.v1.4" hidden="1">Hoja1!$D$22:$G$22</definedName>
-    <definedName name="_xlchart.v1.5" hidden="1">Hoja1!$E$4:$G$4</definedName>
-    <definedName name="_xlchart.v1.6" hidden="1">(Hoja1!$C$4:$C$11,Hoja1!$C$13:$C$20,Hoja1!$C$22:$C$29)</definedName>
-    <definedName name="_xlchart.v1.7" hidden="1">(Hoja1!$H$4:$H$11,Hoja1!$H$13:$H$20,Hoja1!$H$22:$H$29)</definedName>
-    <definedName name="_xlchart.v1.8" hidden="1">Hoja1!$H$3</definedName>
-    <definedName name="_xlchart.v1.9" hidden="1">(Hoja1!$C$4:$C$11,Hoja1!$C$13:$C$20,Hoja1!$C$22:$C$29)</definedName>
+    <definedName name="_xlchart.v1.0" hidden="1">(Hoja1!$C$4:$C$11,Hoja1!$C$13:$C$20,Hoja1!$C$22:$C$29)</definedName>
+    <definedName name="_xlchart.v1.1" hidden="1">(Hoja1!$H$4:$H$11,Hoja1!$H$13:$H$20,Hoja1!$H$22:$H$29)</definedName>
+    <definedName name="_xlchart.v1.2" hidden="1">Hoja1!$H$3</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -137,7 +128,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -364,6 +355,59 @@
             <a:effectLst/>
           </c:spPr>
           <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx2"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="es-MX"/>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525">
+                      <a:solidFill>
+                        <a:schemeClr val="tx2">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
           <c:cat>
             <c:strRef>
               <c:f>Hoja1!$B$4:$B$11</c:f>
@@ -1424,6 +1468,63 @@
             <a:effectLst/>
           </c:spPr>
           <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="es-MX"/>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
           <c:cat>
             <c:strRef>
               <c:f>Hoja1!$B$4:$B$11</c:f>
@@ -1519,6 +1620,63 @@
             <a:effectLst/>
           </c:spPr>
           <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="es-MX"/>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
           <c:cat>
             <c:strRef>
               <c:f>Hoja1!$B$4:$B$11</c:f>
@@ -1898,6 +2056,63 @@
             <a:effectLst/>
           </c:spPr>
           <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="es-MX"/>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
           <c:cat>
             <c:strRef>
               <c:f>Hoja1!$B$13:$B$20</c:f>
@@ -1993,6 +2208,63 @@
             <a:effectLst/>
           </c:spPr>
           <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="es-MX"/>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
           <c:cat>
             <c:strRef>
               <c:f>Hoja1!$B$13:$B$20</c:f>
@@ -2746,10 +3018,10 @@
   <cx:chartData>
     <cx:data id="0">
       <cx:strDim type="cat">
-        <cx:f>_xlchart.v1.6</cx:f>
+        <cx:f>_xlchart.v1.0</cx:f>
       </cx:strDim>
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.7</cx:f>
+        <cx:f>_xlchart.v1.1</cx:f>
       </cx:numDim>
     </cx:data>
   </cx:chartData>
@@ -2787,7 +3059,7 @@
         <cx:series layoutId="boxWhisker" uniqueId="{F7133788-1129-4FB7-B5EE-355D2AD50E0E}">
           <cx:tx>
             <cx:txData>
-              <cx:f>_xlchart.v1.8</cx:f>
+              <cx:f>_xlchart.v1.2</cx:f>
               <cx:v>PORCENTAJE DE PÉRDIDA</cx:v>
             </cx:txData>
           </cx:tx>
@@ -6691,8 +6963,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="53662" y="11314090"/>
-              <a:ext cx="4572000" cy="2743200"/>
+              <a:off x="53662" y="10878247"/>
+              <a:ext cx="4981119" cy="2635340"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -7043,22 +7315,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC5ECB90-EE67-49F2-B71E-283C8DA9AB5B}">
   <dimension ref="A3:L51"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="11.5546875" customWidth="1"/>
-    <col min="2" max="2" width="25.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="25.44140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="26.44140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="25.6640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="30.44140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="17.44140625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="28.109375" customWidth="1"/>
-    <col min="11" max="11" width="30.6640625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="25.77734375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.59765625" customWidth="1"/>
+    <col min="2" max="2" width="25.296875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.09765625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="25.3984375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="26.3984375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.69921875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="30.3984375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="17.3984375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="28.09765625" customWidth="1"/>
+    <col min="11" max="11" width="30.69921875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="25.796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:12" ht="18" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:12" ht="17.399999999999999">
       <c r="A3" s="4" t="s">
         <v>18</v>
       </c>
@@ -7096,7 +7368,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12">
       <c r="A4" s="1">
         <v>1</v>
       </c>
@@ -7140,7 +7412,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12">
       <c r="A5" s="1">
         <v>2</v>
       </c>
@@ -7184,7 +7456,7 @@
         <v>0.98666666666666669</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12">
       <c r="A6" s="1">
         <v>3</v>
       </c>
@@ -7228,7 +7500,7 @@
         <v>0.99534883720930234</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12">
       <c r="A7" s="1">
         <v>4</v>
       </c>
@@ -7272,7 +7544,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:12">
       <c r="A8" s="1">
         <v>5</v>
       </c>
@@ -7316,7 +7588,7 @@
         <v>0.99425287356321834</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:12">
       <c r="A9" s="1">
         <v>6</v>
       </c>
@@ -7360,7 +7632,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:12">
       <c r="A10" s="1">
         <v>7</v>
       </c>
@@ -7404,7 +7676,7 @@
         <v>0.98484848484848486</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:12">
       <c r="A11" s="1">
         <v>8</v>
       </c>
@@ -7448,7 +7720,7 @@
         <v>0.96</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:12">
       <c r="A12" s="1"/>
       <c r="B12" s="1" t="s">
         <v>0</v>
@@ -7468,7 +7740,7 @@
       <c r="K12" s="5"/>
       <c r="L12" s="10"/>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:12">
       <c r="A13" s="2">
         <v>9</v>
       </c>
@@ -7512,7 +7784,7 @@
         <v>0.83823529411764708</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:12">
       <c r="A14" s="2">
         <v>10</v>
       </c>
@@ -7556,7 +7828,7 @@
         <v>0.96610169491525422</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:12">
       <c r="A15" s="2">
         <v>11</v>
       </c>
@@ -7600,7 +7872,7 @@
         <v>0.97560975609756095</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:12">
       <c r="A16" s="2">
         <v>12</v>
       </c>
@@ -7644,7 +7916,7 @@
         <v>0.93</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:12">
       <c r="A17" s="2">
         <v>13</v>
       </c>
@@ -7688,7 +7960,7 @@
         <v>0.99056603773584906</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:12">
       <c r="A18" s="2">
         <v>14</v>
       </c>
@@ -7732,7 +8004,7 @@
         <v>0.97359735973597361</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:12">
       <c r="A19" s="2">
         <v>15</v>
       </c>
@@ -7776,7 +8048,7 @@
         <v>0.96153846153846156</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:12">
       <c r="A20" s="2">
         <v>16</v>
       </c>
@@ -7820,7 +8092,7 @@
         <v>0.96153846153846156</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:12">
       <c r="A21" s="2"/>
       <c r="B21" s="2" t="s">
         <v>0</v>
@@ -7840,7 +8112,7 @@
       <c r="K21" s="6"/>
       <c r="L21" s="6"/>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:12">
       <c r="A22" s="3">
         <v>17</v>
       </c>
@@ -7884,7 +8156,7 @@
         <v>0.95</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:12">
       <c r="A23" s="3">
         <v>18</v>
       </c>
@@ -7928,7 +8200,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:12">
       <c r="A24" s="3">
         <v>19</v>
       </c>
@@ -7972,7 +8244,7 @@
         <v>0.995</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:12">
       <c r="A25" s="3">
         <v>20</v>
       </c>
@@ -8016,7 +8288,7 @@
         <v>0.97368421052631582</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:12">
       <c r="A26" s="3">
         <v>21</v>
       </c>
@@ -8060,7 +8332,7 @@
         <v>0.98421052631578942</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:12">
       <c r="A27" s="3">
         <v>22</v>
       </c>
@@ -8104,7 +8376,7 @@
         <v>0.98930481283422456</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:12">
       <c r="A28" s="3">
         <v>23</v>
       </c>
@@ -8148,7 +8420,7 @@
         <v>0.98994974874371855</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:12">
       <c r="A29" s="3">
         <v>24</v>
       </c>
@@ -8192,7 +8464,7 @@
         <v>0.995</v>
       </c>
     </row>
-    <row r="51" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="51" spans="3:3">
       <c r="C51" t="s">
         <v>25</v>
       </c>

--- a/PRUEBAS DE CONFIANZA.xlsx
+++ b/PRUEBAS DE CONFIANZA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\omich\Documents\SolucionesEnergeticasParaWSN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD53621D-E13A-4CC6-B5BA-216BF938F714}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40EAB052-DE0F-49D2-8372-D89A9AA3552D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{FF7E538C-BC1E-4233-9CFA-651CC43E1462}"/>
   </bookViews>
@@ -16,18 +16,9 @@
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlchart.v1.0" hidden="1">Hoja1!$A$13:$C$13</definedName>
-    <definedName name="_xlchart.v1.1" hidden="1">Hoja1!$A$22:$C$22</definedName>
-    <definedName name="_xlchart.v1.10" hidden="1">(Hoja1!$H$4:$H$11,Hoja1!$H$13:$H$20,Hoja1!$H$22:$H$29)</definedName>
-    <definedName name="_xlchart.v1.11" hidden="1">Hoja1!$H$3</definedName>
-    <definedName name="_xlchart.v1.2" hidden="1">Hoja1!$B$4:$D$4</definedName>
-    <definedName name="_xlchart.v1.3" hidden="1">Hoja1!$D$13:$G$13</definedName>
-    <definedName name="_xlchart.v1.4" hidden="1">Hoja1!$D$22:$G$22</definedName>
-    <definedName name="_xlchart.v1.5" hidden="1">Hoja1!$E$4:$G$4</definedName>
-    <definedName name="_xlchart.v1.6" hidden="1">(Hoja1!$C$4:$C$11,Hoja1!$C$13:$C$20,Hoja1!$C$22:$C$29)</definedName>
-    <definedName name="_xlchart.v1.7" hidden="1">(Hoja1!$H$4:$H$11,Hoja1!$H$13:$H$20,Hoja1!$H$22:$H$29)</definedName>
-    <definedName name="_xlchart.v1.8" hidden="1">Hoja1!$H$3</definedName>
-    <definedName name="_xlchart.v1.9" hidden="1">(Hoja1!$C$4:$C$11,Hoja1!$C$13:$C$20,Hoja1!$C$22:$C$29)</definedName>
+    <definedName name="_xlchart.v1.0" hidden="1">(Hoja1!$C$4:$C$11,Hoja1!$C$13:$C$20,Hoja1!$C$22:$C$29)</definedName>
+    <definedName name="_xlchart.v1.1" hidden="1">(Hoja1!$H$4:$H$11,Hoja1!$H$13:$H$20,Hoja1!$H$22:$H$29)</definedName>
+    <definedName name="_xlchart.v1.2" hidden="1">Hoja1!$H$3</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -225,7 +216,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -241,6 +232,7 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -364,6 +356,60 @@
             <a:effectLst/>
           </c:spPr>
           <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx2"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="es-MX"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525">
+                      <a:solidFill>
+                        <a:schemeClr val="tx2">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
           <c:cat>
             <c:strRef>
               <c:f>Hoja1!$B$4:$B$11</c:f>
@@ -424,7 +470,7 @@
                   <c:v>1.5151515151515151</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>4</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -436,8 +482,9 @@
           </c:extLst>
         </c:ser>
         <c:dLbls>
+          <c:dLblPos val="outEnd"/>
           <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
+          <c:showVal val="1"/>
           <c:showCatName val="0"/>
           <c:showSerName val="0"/>
           <c:showPercent val="0"/>
@@ -735,6 +782,60 @@
             <a:effectLst/>
           </c:spPr>
           <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx2"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="es-MX"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="ctr"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525">
+                      <a:solidFill>
+                        <a:schemeClr val="tx2">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
           <c:cat>
             <c:strRef>
               <c:f>Hoja1!$B$13:$B$20</c:f>
@@ -807,8 +908,9 @@
           </c:extLst>
         </c:ser>
         <c:dLbls>
+          <c:dLblPos val="ctr"/>
           <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
+          <c:showVal val="1"/>
           <c:showCatName val="0"/>
           <c:showSerName val="0"/>
           <c:showPercent val="0"/>
@@ -1042,7 +1144,17 @@
     </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
-      <c:layout/>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="8.546034714541749E-2"/>
+          <c:y val="0.19569039297600238"/>
+          <c:w val="0.88404694349332069"/>
+          <c:h val="0.6013008804481742"/>
+        </c:manualLayout>
+      </c:layout>
       <c:barChart>
         <c:barDir val="col"/>
         <c:grouping val="clustered"/>
@@ -1083,6 +1195,60 @@
             <a:effectLst/>
           </c:spPr>
           <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx2"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="es-MX"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525">
+                      <a:solidFill>
+                        <a:schemeClr val="tx2">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
           <c:cat>
             <c:strRef>
               <c:f>Hoja1!$B$22:$B$29</c:f>
@@ -1155,8 +1321,9 @@
           </c:extLst>
         </c:ser>
         <c:dLbls>
+          <c:dLblPos val="outEnd"/>
           <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
+          <c:showVal val="1"/>
           <c:showCatName val="0"/>
           <c:showSerName val="0"/>
           <c:showPercent val="0"/>
@@ -1424,6 +1591,64 @@
             <a:effectLst/>
           </c:spPr>
           <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="es-MX"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="ctr"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
           <c:cat>
             <c:strRef>
               <c:f>Hoja1!$B$4:$B$11</c:f>
@@ -1484,7 +1709,7 @@
                   <c:v>130</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>192</c:v>
+                  <c:v>200</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1519,6 +1744,64 @@
             <a:effectLst/>
           </c:spPr>
           <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="es-MX"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="ctr"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
           <c:cat>
             <c:strRef>
               <c:f>Hoja1!$B$4:$B$11</c:f>
@@ -1579,7 +1862,7 @@
                   <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>8</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1591,8 +1874,9 @@
           </c:extLst>
         </c:ser>
         <c:dLbls>
+          <c:dLblPos val="ctr"/>
           <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
+          <c:showVal val="1"/>
           <c:showCatName val="0"/>
           <c:showSerName val="0"/>
           <c:showPercent val="0"/>
@@ -1898,6 +2182,64 @@
             <a:effectLst/>
           </c:spPr>
           <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="es-MX"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="ctr"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
           <c:cat>
             <c:strRef>
               <c:f>Hoja1!$B$13:$B$20</c:f>
@@ -1993,6 +2335,64 @@
             <a:effectLst/>
           </c:spPr>
           <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="es-MX"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="ctr"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
           <c:cat>
             <c:strRef>
               <c:f>Hoja1!$B$13:$B$20</c:f>
@@ -2065,8 +2465,9 @@
           </c:extLst>
         </c:ser>
         <c:dLbls>
+          <c:dLblPos val="ctr"/>
           <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
+          <c:showVal val="1"/>
           <c:showCatName val="0"/>
           <c:showSerName val="0"/>
           <c:showPercent val="0"/>
@@ -2372,6 +2773,64 @@
             <a:effectLst/>
           </c:spPr>
           <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="es-MX"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="ctr"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
           <c:cat>
             <c:strRef>
               <c:f>Hoja1!$B$22:$B$29</c:f>
@@ -2467,6 +2926,64 @@
             <a:effectLst/>
           </c:spPr>
           <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="es-MX"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="ctr"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
           <c:cat>
             <c:strRef>
               <c:f>Hoja1!$B$22:$B$29</c:f>
@@ -2539,8 +3056,9 @@
           </c:extLst>
         </c:ser>
         <c:dLbls>
+          <c:dLblPos val="ctr"/>
           <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
+          <c:showVal val="1"/>
           <c:showCatName val="0"/>
           <c:showSerName val="0"/>
           <c:showPercent val="0"/>
@@ -2741,15 +3259,1253 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="es-ES"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" cap="all" spc="120" normalizeH="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="es-MX"/>
+              <a:t>NRF vs XBee vs LoRa Básico</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" cap="all" spc="120" normalizeH="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="es-MX"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Hoja1!$C$4</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>NRF24L01</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="50000"/>
+                        <a:lumOff val="50000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="es-MX"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>(Hoja1!$E$3:$F$3,Hoja1!$H$3)</c:f>
+              <c:strCache>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>PAQUETES ENVIADOS</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>PAQUETES RECIBIDOS</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>PORCENTAJE DE PÉRDIDA</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>(Hoja1!$E$4:$F$4,Hoja1!$H$4)</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>199</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>199</c:v>
+                </c:pt>
+                <c:pt idx="2" formatCode="0.00">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-A12B-42F7-BB9E-907B91BFEDF1}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Hoja1!$C$13</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>XBEE</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="50000"/>
+                        <a:lumOff val="50000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="es-MX"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>(Hoja1!$E$3:$F$3,Hoja1!$H$3)</c:f>
+              <c:strCache>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>PAQUETES ENVIADOS</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>PAQUETES RECIBIDOS</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>PORCENTAJE DE PÉRDIDA</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>(Hoja1!$E$13:$F$13,Hoja1!$H$13)</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>204</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>171</c:v>
+                </c:pt>
+                <c:pt idx="2" formatCode="0.00">
+                  <c:v>16.176470588235293</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-A12B-42F7-BB9E-907B91BFEDF1}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Hoja1!$C$22</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>LoRa</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent3"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="50000"/>
+                        <a:lumOff val="50000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="es-MX"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>(Hoja1!$E$3:$F$3,Hoja1!$H$3)</c:f>
+              <c:strCache>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>PAQUETES ENVIADOS</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>PAQUETES RECIBIDOS</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>PORCENTAJE DE PÉRDIDA</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>(Hoja1!$E$22:$F$22,Hoja1!$H$22)</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>200</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>190</c:v>
+                </c:pt>
+                <c:pt idx="2" formatCode="0.00">
+                  <c:v>5</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-A12B-42F7-BB9E-907B91BFEDF1}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:dLblPos val="outEnd"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="444"/>
+        <c:overlap val="-90"/>
+        <c:axId val="1033180176"/>
+        <c:axId val="1308595024"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1033180176"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="800" b="0" i="0" u="none" strike="noStrike" kern="1200" cap="all" spc="120" normalizeH="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-MX"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1308595024"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1308595024"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="1"/>
+        <c:axPos val="l"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="1033180176"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="t"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="es-MX"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="lt1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="es-MX"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="es-ES"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" cap="all" spc="120" normalizeH="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="es-MX"/>
+              <a:t>Título NRF vs XBee vs LoRa mejoras</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" cap="all" spc="120" normalizeH="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="es-MX"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Hoja1!$C$11</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>NRF24L01</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="50000"/>
+                        <a:lumOff val="50000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="es-MX"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>(Hoja1!$E$3:$F$3,Hoja1!$H$3)</c:f>
+              <c:strCache>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>PAQUETES ENVIADOS</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>PAQUETES RECIBIDOS</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>PORCENTAJE DE PÉRDIDA</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>(Hoja1!$E$11:$F$11,Hoja1!$H$11)</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>200</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>200</c:v>
+                </c:pt>
+                <c:pt idx="2" formatCode="0.00">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-1F53-4ECE-8159-ED4D5173D661}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Hoja1!$C$20</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>XBEE</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="50000"/>
+                        <a:lumOff val="50000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="es-MX"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>(Hoja1!$E$3:$F$3,Hoja1!$H$3)</c:f>
+              <c:strCache>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>PAQUETES ENVIADOS</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>PAQUETES RECIBIDOS</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>PORCENTAJE DE PÉRDIDA</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>(Hoja1!$E$20:$F$20,Hoja1!$H$20)</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>208</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>200</c:v>
+                </c:pt>
+                <c:pt idx="2" formatCode="0.00">
+                  <c:v>3.8461538461538463</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-1F53-4ECE-8159-ED4D5173D661}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Hoja1!$C$29</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>LoRa</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent3"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="50000"/>
+                        <a:lumOff val="50000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="es-MX"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>(Hoja1!$E$3:$F$3,Hoja1!$H$3)</c:f>
+              <c:strCache>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>PAQUETES ENVIADOS</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>PAQUETES RECIBIDOS</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>PORCENTAJE DE PÉRDIDA</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>(Hoja1!$E$29:$F$29,Hoja1!$H$29)</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>200</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>199</c:v>
+                </c:pt>
+                <c:pt idx="2" formatCode="0.00">
+                  <c:v>0.5</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-1F53-4ECE-8159-ED4D5173D661}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:dLblPos val="outEnd"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="444"/>
+        <c:overlap val="-90"/>
+        <c:axId val="1134102928"/>
+        <c:axId val="1134101968"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1134102928"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="800" b="0" i="0" u="none" strike="noStrike" kern="1200" cap="all" spc="120" normalizeH="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-MX"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1134101968"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1134101968"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="1"/>
+        <c:axPos val="l"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="1134102928"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="t"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="es-MX"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="lt1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="es-MX"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
 <file path=xl/charts/chartEx1.xml><?xml version="1.0" encoding="utf-8"?>
 <cx:chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex">
   <cx:chartData>
     <cx:data id="0">
       <cx:strDim type="cat">
-        <cx:f>_xlchart.v1.6</cx:f>
+        <cx:f>_xlchart.v1.0</cx:f>
       </cx:strDim>
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.7</cx:f>
+        <cx:f>_xlchart.v1.1</cx:f>
       </cx:numDim>
     </cx:data>
   </cx:chartData>
@@ -2787,7 +4543,7 @@
         <cx:series layoutId="boxWhisker" uniqueId="{F7133788-1129-4FB7-B5EE-355D2AD50E0E}">
           <cx:tx>
             <cx:txData>
-              <cx:f>_xlchart.v1.8</cx:f>
+              <cx:f>_xlchart.v1.2</cx:f>
               <cx:v>PORCENTAJE DE PÉRDIDA</cx:v>
             </cx:txData>
           </cx:tx>
@@ -2991,6 +4747,86 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors8.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors9.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="207">
   <cs:axisTitle>
@@ -6426,20 +8262,1068 @@
 </cs:chartStyle>
 </file>
 
+<file path=xl/charts/style8.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="202">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200" cap="all"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="800" kern="1200" cap="all" spc="120" normalizeH="0" baseline="0"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="50000"/>
+        <a:lumOff val="50000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0"/>
+    <cs:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="22225" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout size="6"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1600" b="1" kern="1200" cap="all" spc="120" normalizeH="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="800" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style9.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="202">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200" cap="all"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="800" kern="1200" cap="all" spc="120" normalizeH="0" baseline="0"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="50000"/>
+        <a:lumOff val="50000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0"/>
+    <cs:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="22225" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout size="6"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1600" b="1" kern="1200" cap="all" spc="120" normalizeH="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="800" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>987380</xdr:colOff>
+      <xdr:colOff>257577</xdr:colOff>
       <xdr:row>30</xdr:row>
-      <xdr:rowOff>53662</xdr:rowOff>
+      <xdr:rowOff>32197</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>692631</xdr:colOff>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>1894659</xdr:colOff>
       <xdr:row>44</xdr:row>
-      <xdr:rowOff>182450</xdr:rowOff>
+      <xdr:rowOff>160985</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -6467,15 +9351,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>994318</xdr:colOff>
-      <xdr:row>29</xdr:row>
-      <xdr:rowOff>180279</xdr:rowOff>
+      <xdr:colOff>683079</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>8560</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>557562</xdr:colOff>
+      <xdr:colOff>246323</xdr:colOff>
       <xdr:row>44</xdr:row>
-      <xdr:rowOff>135674</xdr:rowOff>
+      <xdr:rowOff>146406</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -6503,15 +9387,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
+      <xdr:colOff>64395</xdr:colOff>
       <xdr:row>30</xdr:row>
-      <xdr:rowOff>13010</xdr:rowOff>
+      <xdr:rowOff>2277</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>631902</xdr:colOff>
+      <xdr:colOff>696297</xdr:colOff>
       <xdr:row>44</xdr:row>
-      <xdr:rowOff>154259</xdr:rowOff>
+      <xdr:rowOff>143526</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -6691,8 +9575,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="53662" y="11314090"/>
-              <a:ext cx="4572000" cy="2743200"/>
+              <a:off x="53662" y="11343067"/>
+              <a:ext cx="4569639" cy="2749640"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -6720,6 +9604,78 @@
         </xdr:sp>
       </mc:Fallback>
     </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>1320083</xdr:colOff>
+      <xdr:row>62</xdr:row>
+      <xdr:rowOff>88007</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>568815</xdr:colOff>
+      <xdr:row>77</xdr:row>
+      <xdr:rowOff>94446</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="6" name="Gráfico 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{858FA5CF-CC7F-770A-E4B3-C69035FD5618}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId8"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>1244957</xdr:colOff>
+      <xdr:row>62</xdr:row>
+      <xdr:rowOff>55808</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>601014</xdr:colOff>
+      <xdr:row>77</xdr:row>
+      <xdr:rowOff>62247</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="7" name="Gráfico 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E97FB3F6-34A1-6CF2-E640-4435587E366B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId9"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
@@ -7042,7 +9998,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC5ECB90-EE67-49F2-B71E-283C8DA9AB5B}">
-  <dimension ref="A3:L51"/>
+  <dimension ref="A3:L71"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.5546875" customWidth="1"/>
@@ -7421,31 +10377,31 @@
         <v>200</v>
       </c>
       <c r="F11" s="1">
-        <v>192</v>
+        <v>200</v>
       </c>
       <c r="G11" s="1">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H11" s="5">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I11" s="5">
         <f t="shared" si="2"/>
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="J11" s="1">
         <f t="shared" si="3"/>
-        <v>19.2</v>
+        <v>20</v>
       </c>
       <c r="K11" s="5">
         <f t="shared" si="4"/>
-        <v>0.32</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="L11" s="10">
         <f t="shared" si="5"/>
-        <v>0.96</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.3">
@@ -8197,6 +11153,9 @@
         <v>25</v>
       </c>
     </row>
+    <row r="71" spans="12:12" x14ac:dyDescent="0.3">
+      <c r="L71" s="11"/>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/PRUEBAS DE CONFIANZA.xlsx
+++ b/PRUEBAS DE CONFIANZA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\omich\Documents\SolucionesEnergeticasParaWSN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40EAB052-DE0F-49D2-8372-D89A9AA3552D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88EC254F-F5C9-4BB0-8ADB-B749F535FF54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{FF7E538C-BC1E-4233-9CFA-651CC43E1462}"/>
   </bookViews>
@@ -19,6 +19,12 @@
     <definedName name="_xlchart.v1.0" hidden="1">(Hoja1!$C$4:$C$11,Hoja1!$C$13:$C$20,Hoja1!$C$22:$C$29)</definedName>
     <definedName name="_xlchart.v1.1" hidden="1">(Hoja1!$H$4:$H$11,Hoja1!$H$13:$H$20,Hoja1!$H$22:$H$29)</definedName>
     <definedName name="_xlchart.v1.2" hidden="1">Hoja1!$H$3</definedName>
+    <definedName name="_xlchart.v1.3" hidden="1">(Hoja1!$C$4:$C$11,Hoja1!$C$13:$C$20,Hoja1!$C$22:$C$29)</definedName>
+    <definedName name="_xlchart.v1.4" hidden="1">(Hoja1!$H$4:$H$11,Hoja1!$H$13:$H$20,Hoja1!$H$22:$H$29)</definedName>
+    <definedName name="_xlchart.v1.5" hidden="1">Hoja1!$H$3</definedName>
+    <definedName name="_xlchart.v1.6" hidden="1">(Hoja1!$C$4:$C$11,Hoja1!$C$13:$C$20,Hoja1!$C$22:$C$29)</definedName>
+    <definedName name="_xlchart.v1.7" hidden="1">(Hoja1!$H$4:$H$11,Hoja1!$H$13:$H$20,Hoja1!$H$22:$H$29)</definedName>
+    <definedName name="_xlchart.v1.8" hidden="1">Hoja1!$H$3</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -44,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="27">
   <si>
     <t>SOFTWARE</t>
   </si>
@@ -122,6 +128,9 @@
   </si>
   <si>
     <t>|</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
   </si>
 </sst>
 </file>
@@ -216,7 +225,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -233,6 +242,7 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -461,7 +471,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.57471264367816088</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>0</c:v>
@@ -604,34 +614,6 @@
         <a:effectLst/>
       </c:spPr>
     </c:plotArea>
-    <c:legend>
-      <c:legendPos val="b"/>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx2"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="es-MX"/>
-        </a:p>
-      </c:txPr>
-    </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
     <c:extLst>
@@ -929,7 +911,7 @@
         <c:delete val="0"/>
         <c:axPos val="b"/>
         <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
+        <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:spPr>
@@ -991,7 +973,7 @@
           </c:spPr>
         </c:majorGridlines>
         <c:numFmt formatCode="0.00" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
+        <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:spPr>
@@ -1342,7 +1324,7 @@
         <c:delete val="0"/>
         <c:axPos val="b"/>
         <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
+        <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:spPr>
@@ -1404,7 +1386,7 @@
           </c:spPr>
         </c:majorGridlines>
         <c:numFmt formatCode="0.00" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
+        <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:spPr>
@@ -1688,7 +1670,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="8"/>
                 <c:pt idx="0">
-                  <c:v>199</c:v>
+                  <c:v>200</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>148</c:v>
@@ -1700,7 +1682,7 @@
                   <c:v>138</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>346</c:v>
+                  <c:v>198</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>198</c:v>
@@ -3440,10 +3422,10 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>199</c:v>
+                  <c:v>200</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>199</c:v>
+                  <c:v>200</c:v>
                 </c:pt>
                 <c:pt idx="2" formatCode="0.00">
                   <c:v>0</c:v>
@@ -9316,14 +9298,14 @@
     <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>257577</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>32197</xdr:rowOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>180047</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>1894659</xdr:colOff>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>113731</xdr:colOff>
       <xdr:row>44</xdr:row>
-      <xdr:rowOff>160985</xdr:rowOff>
+      <xdr:rowOff>170596</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -9353,13 +9335,13 @@
       <xdr:col>4</xdr:col>
       <xdr:colOff>683079</xdr:colOff>
       <xdr:row>30</xdr:row>
-      <xdr:rowOff>8560</xdr:rowOff>
+      <xdr:rowOff>8559</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>246323</xdr:colOff>
+      <xdr:colOff>227463</xdr:colOff>
       <xdr:row>44</xdr:row>
-      <xdr:rowOff>146406</xdr:rowOff>
+      <xdr:rowOff>170596</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -9998,7 +9980,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC5ECB90-EE67-49F2-B71E-283C8DA9AB5B}">
-  <dimension ref="A3:L71"/>
+  <dimension ref="A3:M71"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.5546875" customWidth="1"/>
@@ -10007,11 +9989,11 @@
     <col min="5" max="5" width="25.44140625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="26.44140625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="25.6640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="30.44140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="17.44140625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="28.109375" customWidth="1"/>
-    <col min="11" max="11" width="30.6640625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="25.77734375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="29.6640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="17" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="27.33203125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="29.77734375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="25.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="3" spans="1:12" ht="18" x14ac:dyDescent="0.35">
@@ -10066,10 +10048,10 @@
         <v>15</v>
       </c>
       <c r="E4" s="1">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F4" s="1">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="G4" s="1">
         <f>E4-F4</f>
@@ -10085,11 +10067,11 @@
       </c>
       <c r="J4" s="1">
         <f>F4/10</f>
-        <v>19.899999999999999</v>
+        <v>20</v>
       </c>
       <c r="K4" s="5">
         <f>F4 / 600</f>
-        <v>0.33166666666666667</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="L4" s="10">
         <f>F4/E4</f>
@@ -10242,10 +10224,10 @@
         <v>15</v>
       </c>
       <c r="E8" s="1">
-        <v>348</v>
+        <v>200</v>
       </c>
       <c r="F8" s="1">
-        <v>346</v>
+        <v>198</v>
       </c>
       <c r="G8" s="1">
         <f t="shared" si="0"/>
@@ -10253,23 +10235,23 @@
       </c>
       <c r="H8" s="5">
         <f t="shared" si="1"/>
-        <v>0.57471264367816088</v>
+        <v>1</v>
       </c>
       <c r="I8" s="5">
         <f t="shared" si="2"/>
-        <v>99.425287356321846</v>
+        <v>99</v>
       </c>
       <c r="J8" s="1">
         <f t="shared" si="3"/>
-        <v>34.6</v>
+        <v>19.8</v>
       </c>
       <c r="K8" s="5">
         <f t="shared" si="4"/>
-        <v>0.57666666666666666</v>
+        <v>0.33</v>
       </c>
       <c r="L8" s="10">
         <f t="shared" si="5"/>
-        <v>0.99425287356321834</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.3">
@@ -10380,7 +10362,7 @@
         <v>200</v>
       </c>
       <c r="G11" s="1">
-        <f t="shared" si="0"/>
+        <f>E11-F11</f>
         <v>0</v>
       </c>
       <c r="H11" s="5">
@@ -10752,7 +10734,7 @@
         <v>200</v>
       </c>
       <c r="G20" s="2">
-        <f t="shared" si="0"/>
+        <f>E20-F20</f>
         <v>8</v>
       </c>
       <c r="H20" s="6">
@@ -11146,6 +11128,19 @@
       <c r="L29" s="7">
         <f t="shared" si="5"/>
         <v>0.995</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="K30" s="12"/>
+    </row>
+    <row r="47" spans="12:13" x14ac:dyDescent="0.3">
+      <c r="M47" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="48" spans="12:13" x14ac:dyDescent="0.3">
+      <c r="L48" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="51" spans="3:3" x14ac:dyDescent="0.3">

--- a/PRUEBAS DE CONFIANZA.xlsx
+++ b/PRUEBAS DE CONFIANZA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\omich\Documents\SolucionesEnergeticasParaWSN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88EC254F-F5C9-4BB0-8ADB-B749F535FF54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB80D344-56CE-4CF9-AFE8-418952677662}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{FF7E538C-BC1E-4233-9CFA-651CC43E1462}"/>
   </bookViews>
@@ -19,12 +19,6 @@
     <definedName name="_xlchart.v1.0" hidden="1">(Hoja1!$C$4:$C$11,Hoja1!$C$13:$C$20,Hoja1!$C$22:$C$29)</definedName>
     <definedName name="_xlchart.v1.1" hidden="1">(Hoja1!$H$4:$H$11,Hoja1!$H$13:$H$20,Hoja1!$H$22:$H$29)</definedName>
     <definedName name="_xlchart.v1.2" hidden="1">Hoja1!$H$3</definedName>
-    <definedName name="_xlchart.v1.3" hidden="1">(Hoja1!$C$4:$C$11,Hoja1!$C$13:$C$20,Hoja1!$C$22:$C$29)</definedName>
-    <definedName name="_xlchart.v1.4" hidden="1">(Hoja1!$H$4:$H$11,Hoja1!$H$13:$H$20,Hoja1!$H$22:$H$29)</definedName>
-    <definedName name="_xlchart.v1.5" hidden="1">Hoja1!$H$3</definedName>
-    <definedName name="_xlchart.v1.6" hidden="1">(Hoja1!$C$4:$C$11,Hoja1!$C$13:$C$20,Hoja1!$C$22:$C$29)</definedName>
-    <definedName name="_xlchart.v1.7" hidden="1">(Hoja1!$H$4:$H$11,Hoja1!$H$13:$H$20,Hoja1!$H$22:$H$29)</definedName>
-    <definedName name="_xlchart.v1.8" hidden="1">Hoja1!$H$3</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -3895,7 +3889,7 @@
             </a:pPr>
             <a:r>
               <a:rPr lang="es-MX"/>
-              <a:t>Título NRF vs XBee vs LoRa mejoras</a:t>
+              <a:t> NRF vs XBee vs LoRa mejoras</a:t>
             </a:r>
           </a:p>
         </c:rich>
